--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487205_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487205_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.2968</v>
+        <v>5.0424</v>
       </c>
       <c r="E2" t="n">
-        <v>5.18</v>
+        <v>6.0594</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.8832</v>
+        <v>-1.017</v>
       </c>
       <c r="G2" t="n">
         <v>6.2887</v>
@@ -610,13 +610,13 @@
         <v>1.3511</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.741</v>
+        <v>0.0046</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.2942</v>
+        <v>-0.4147</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5532</v>
+        <v>0.4194</v>
       </c>
       <c r="V2" t="n">
         <v>-0.2859</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S. CAMPBELL</t>
+          <t>M. MENDEZ MADERA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.3599</v>
+        <v>1.8849</v>
       </c>
       <c r="E3" t="n">
-        <v>3.5365</v>
+        <v>1.9004</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.1765</v>
+        <v>-0.0155</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.3878</v>
+        <v>2.1482</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6321</v>
+        <v>0.828</v>
       </c>
       <c r="I3" t="n">
-        <v>-2.02</v>
+        <v>1.3202</v>
       </c>
       <c r="J3" t="n">
-        <v>1.5546</v>
+        <v>2.0614</v>
       </c>
       <c r="K3" t="n">
-        <v>2.4421</v>
+        <v>1.4023</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.8875</v>
+        <v>0.6591</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.9424</v>
+        <v>0.0868</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.8099</v>
+        <v>-0.5743</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.1325</v>
+        <v>0.6612</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.5441</v>
+        <v>1.3511</v>
       </c>
       <c r="Q3" t="n">
-        <v>-3.2811</v>
+        <v>-0.193</v>
       </c>
       <c r="R3" t="n">
-        <v>1.7371</v>
+        <v>1.5441</v>
       </c>
       <c r="S3" t="n">
-        <v>5.6779</v>
+        <v>-0.1005</v>
       </c>
       <c r="T3" t="n">
-        <v>3.7492</v>
+        <v>0.0321</v>
       </c>
       <c r="U3" t="n">
-        <v>1.9287</v>
+        <v>-0.1325</v>
       </c>
       <c r="V3" t="n">
-        <v>0.614</v>
+        <v>-1.5138</v>
       </c>
       <c r="W3" t="n">
-        <v>1.5138</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.8999</v>
+        <v>-1.5138</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. MENDEZ MADERA</t>
+          <t>V. OVANDO TORRETTA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.6252</v>
+        <v>-0.0188</v>
       </c>
       <c r="E4" t="n">
-        <v>1.8816</v>
+        <v>-0.0188</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.2564</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>2.1482</v>
+        <v>0.0407</v>
       </c>
       <c r="H4" t="n">
-        <v>0.828</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>1.3202</v>
+        <v>0.0407</v>
       </c>
       <c r="J4" t="n">
-        <v>2.0614</v>
+        <v>0.0407</v>
       </c>
       <c r="K4" t="n">
-        <v>1.4023</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6591</v>
+        <v>0.0407</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0868</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.5743</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>0.6612</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.3511</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.193</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.5441</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3602</v>
+        <v>-0.0595</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0132</v>
+        <v>-0.0595</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3735</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.5138</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.5138</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>V. OVANDO TORRETTA</t>
+          <t>H. BARREIRO ESCARCEGA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,58 +799,58 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.0188</v>
+        <v>-0.6521</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0188</v>
+        <v>-0.0896</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>-0.5626</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0407</v>
+        <v>-0.5963000000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>-0.712</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0407</v>
+        <v>0.1157</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0407</v>
+        <v>0.2049</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>0.0828</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0407</v>
+        <v>0.1221</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>-0.8012</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>-0.7948</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>-0.0064</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>0.386</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-0.193</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>0.579</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0595</v>
+        <v>-0.4419</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0595</v>
+        <v>-0.1014</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>-0.3404</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>H. BARREIRO ESCARCEGA</t>
+          <t>S. CAMPBELL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.1727</v>
+        <v>-0.7914</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.4495</v>
+        <v>0.67</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.7232</v>
+        <v>-1.4614</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.5963000000000001</v>
+        <v>-1.3878</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.712</v>
+        <v>0.6321</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1157</v>
+        <v>-2.02</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2049</v>
+        <v>1.5546</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0828</v>
+        <v>2.4421</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1221</v>
+        <v>-0.8875</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.8012</v>
+        <v>-2.9424</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.7948</v>
+        <v>-1.8099</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.0064</v>
+        <v>-1.1325</v>
       </c>
       <c r="P6" t="n">
-        <v>0.386</v>
+        <v>-1.5441</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.193</v>
+        <v>-3.2811</v>
       </c>
       <c r="R6" t="n">
-        <v>0.579</v>
+        <v>1.7371</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.9624</v>
+        <v>1.5265</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4614</v>
+        <v>0.8828</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.501</v>
+        <v>0.6437</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.614</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.5138</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.8999</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. QUIÑONES CASTRO</t>
+          <t>I. VILLAVERDE GONZALEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.1677</v>
+        <v>-1.5536</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.1309</v>
+        <v>0.804</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.0368</v>
+        <v>-2.3576</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.2953</v>
+        <v>2.2641</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.7772</v>
+        <v>1.6487</v>
       </c>
       <c r="I7" t="n">
-        <v>0.482</v>
+        <v>0.6155</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2056</v>
+        <v>2.0374</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1242</v>
+        <v>2.6236</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0814</v>
+        <v>-0.5862000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.5009</v>
+        <v>0.2268</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.9014</v>
+        <v>-0.9749</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4006</v>
+        <v>1.2017</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.386</v>
+        <v>-0.193</v>
       </c>
       <c r="Q7" t="n">
         <v>-1.158</v>
       </c>
       <c r="R7" t="n">
-        <v>0.772</v>
+        <v>0.965</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2584</v>
+        <v>0.0592</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1785</v>
+        <v>-0.07530000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.08</v>
+        <v>0.1345</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.228</v>
+        <v>-3.6839</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.228</v>
+        <v>-3.6839</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>I. VILLAVERDE GONZALEZ</t>
+          <t>J. QUIÑONES CASTRO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.2546</v>
+        <v>-1.787</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3439</v>
+        <v>-0.8305</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.5985</v>
+        <v>-0.9565</v>
       </c>
       <c r="G8" t="n">
-        <v>2.2641</v>
+        <v>-0.2953</v>
       </c>
       <c r="H8" t="n">
-        <v>1.6487</v>
+        <v>-0.7772</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6155</v>
+        <v>0.482</v>
       </c>
       <c r="J8" t="n">
-        <v>2.0374</v>
+        <v>0.2056</v>
       </c>
       <c r="K8" t="n">
-        <v>2.6236</v>
+        <v>0.1242</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.5862000000000001</v>
+        <v>0.0814</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2268</v>
+        <v>-0.5009</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.9749</v>
+        <v>-0.9014</v>
       </c>
       <c r="O8" t="n">
-        <v>1.2017</v>
+        <v>0.4006</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.193</v>
+        <v>-0.386</v>
       </c>
       <c r="Q8" t="n">
         <v>-1.158</v>
       </c>
       <c r="R8" t="n">
-        <v>0.965</v>
+        <v>0.772</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6418</v>
+        <v>0.1223</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5354</v>
+        <v>0.122</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1064</v>
+        <v>0.0003</v>
       </c>
       <c r="V8" t="n">
-        <v>-3.6839</v>
+        <v>-1.228</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-3.6839</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.9784</v>
+        <v>-3.3448</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.9481000000000001</v>
+        <v>-0.5286999999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.0303</v>
+        <v>-2.8162</v>
       </c>
       <c r="G9" t="n">
         <v>-2.0314</v>
@@ -1156,13 +1156,13 @@
         <v>0.193</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.4608</v>
+        <v>-0.8272</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8328</v>
+        <v>-0.4134</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.628</v>
+        <v>-0.4138</v>
       </c>
       <c r="V9" t="n">
         <v>0.2859</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-6.5116</v>
+        <v>-5.6995</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.2199</v>
+        <v>-1.3811</v>
       </c>
       <c r="F10" t="n">
-        <v>-4.2917</v>
+        <v>-4.3185</v>
       </c>
       <c r="G10" t="n">
         <v>0.2927</v>
@@ -1234,13 +1234,13 @@
         <v>0.965</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.5461</v>
+        <v>-0.734</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.4726</v>
+        <v>-0.6339</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.07340000000000001</v>
+        <v>-0.1002</v>
       </c>
       <c r="V10" t="n">
         <v>-2.1701</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-9.668699999999999</v>
+        <v>-8.380699999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.0929</v>
+        <v>-3.3136</v>
       </c>
       <c r="F11" t="n">
-        <v>-5.5757</v>
+        <v>-5.0671</v>
       </c>
       <c r="G11" t="n">
         <v>-6.4932</v>
@@ -1312,13 +1312,13 @@
         <v>0.579</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.2454</v>
+        <v>-0.9574</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.1752</v>
+        <v>-0.3959</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.0702</v>
+        <v>-0.5615</v>
       </c>
       <c r="V11" t="n">
         <v>0.614</v>
@@ -1345,22 +1345,22 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-16.4906</v>
+        <v>-15.3006</v>
       </c>
       <c r="E12" t="n">
-        <v>2.0819</v>
+        <v>3.271500000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>-18.5723</v>
+        <v>-18.5724</v>
       </c>
       <c r="G12" t="n">
-        <v>0.2304000000000004</v>
+        <v>0.2304000000000013</v>
       </c>
       <c r="H12" t="n">
         <v>-5.174799999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>5.405300000000001</v>
+        <v>5.4053</v>
       </c>
       <c r="J12" t="n">
         <v>14.9424</v>
@@ -1387,16 +1387,16 @@
         <v>-15.4405</v>
       </c>
       <c r="R12" t="n">
-        <v>8.6853</v>
+        <v>8.685300000000002</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.5977</v>
+        <v>-1.4079</v>
       </c>
       <c r="T12" t="n">
-        <v>-2.247199999999999</v>
+        <v>-1.0572</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3505999999999999</v>
+        <v>-0.3505</v>
       </c>
       <c r="V12" t="n">
         <v>-7.3678</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>I. SALAZAR ORTEGA</t>
+          <t>G. TSULAIA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,64 +1423,64 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.5494</v>
+        <v>6.3524</v>
       </c>
       <c r="E13" t="n">
-        <v>5.3084</v>
+        <v>5.3353</v>
       </c>
       <c r="F13" t="n">
-        <v>1.2411</v>
+        <v>1.0171</v>
       </c>
       <c r="G13" t="n">
-        <v>3.2835</v>
+        <v>4.0182</v>
       </c>
       <c r="H13" t="n">
-        <v>3.5127</v>
+        <v>3.8325</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2292</v>
+        <v>0.1856</v>
       </c>
       <c r="J13" t="n">
-        <v>4.7174</v>
+        <v>5.1116</v>
       </c>
       <c r="K13" t="n">
-        <v>3.6999</v>
+        <v>3.6792</v>
       </c>
       <c r="L13" t="n">
-        <v>1.0175</v>
+        <v>1.4323</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.4339</v>
+        <v>-1.0934</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.1872</v>
+        <v>0.1533</v>
       </c>
       <c r="O13" t="n">
         <v>-1.2467</v>
       </c>
       <c r="P13" t="n">
-        <v>1.9301</v>
+        <v>1.7371</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.9301</v>
+        <v>1.7371</v>
       </c>
       <c r="S13" t="n">
-        <v>1.3359</v>
+        <v>0.3113</v>
       </c>
       <c r="T13" t="n">
-        <v>0.591</v>
+        <v>-0.0621</v>
       </c>
       <c r="U13" t="n">
-        <v>0.7449</v>
+        <v>0.3734</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.2859</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>0.2859</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>G. TSULAIA</t>
+          <t>I. SALAZAR ORTEGA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.3907</v>
+        <v>6.1152</v>
       </c>
       <c r="E14" t="n">
-        <v>4.5342</v>
+        <v>5.0079</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8565</v>
+        <v>1.1072</v>
       </c>
       <c r="G14" t="n">
-        <v>4.0182</v>
+        <v>3.2835</v>
       </c>
       <c r="H14" t="n">
-        <v>3.8325</v>
+        <v>3.5127</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1856</v>
+        <v>-0.2292</v>
       </c>
       <c r="J14" t="n">
-        <v>5.1116</v>
+        <v>4.7174</v>
       </c>
       <c r="K14" t="n">
-        <v>3.6792</v>
+        <v>3.6999</v>
       </c>
       <c r="L14" t="n">
-        <v>1.4323</v>
+        <v>1.0175</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.0934</v>
+        <v>-1.4339</v>
       </c>
       <c r="N14" t="n">
-        <v>0.1533</v>
+        <v>-0.1872</v>
       </c>
       <c r="O14" t="n">
         <v>-1.2467</v>
       </c>
       <c r="P14" t="n">
-        <v>1.7371</v>
+        <v>1.9301</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.7371</v>
+        <v>1.9301</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.6504</v>
+        <v>0.9016</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.8632</v>
+        <v>0.2905</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2128</v>
+        <v>0.6111</v>
       </c>
       <c r="V14" t="n">
-        <v>0.2859</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>0.2859</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. NDIAYE SOW</t>
+          <t>E. ERRASTI DIEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.7179</v>
+        <v>4.4789</v>
       </c>
       <c r="E15" t="n">
-        <v>4.7908</v>
+        <v>6.5484</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.0729</v>
+        <v>-2.0695</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.7472</v>
+        <v>5.7102</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.2463</v>
+        <v>1.0184</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.5009</v>
+        <v>4.6918</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.3262</v>
+        <v>7.0776</v>
       </c>
       <c r="K15" t="n">
-        <v>0.3414</v>
+        <v>1.4126</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.6676</v>
+        <v>5.6651</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.421</v>
+        <v>-1.3674</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.5878</v>
+        <v>-0.3942</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.8333</v>
+        <v>-0.9732</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.772</v>
+        <v>-0.193</v>
       </c>
       <c r="Q15" t="n">
         <v>-1.9301</v>
       </c>
       <c r="R15" t="n">
-        <v>1.158</v>
+        <v>1.7371</v>
       </c>
       <c r="S15" t="n">
-        <v>1.3253</v>
+        <v>-0.09619999999999999</v>
       </c>
       <c r="T15" t="n">
-        <v>0.6214</v>
+        <v>-0.113</v>
       </c>
       <c r="U15" t="n">
-        <v>0.7039</v>
+        <v>0.0168</v>
       </c>
       <c r="V15" t="n">
-        <v>4.9119</v>
+        <v>-0.9421</v>
       </c>
       <c r="W15" t="n">
-        <v>6.4257</v>
+        <v>1.5138</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.5138</v>
+        <v>-2.4559</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>E. ERRASTI DIEZ</t>
+          <t>I. CHACON RODRIGUEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.6371</v>
+        <v>2.9257</v>
       </c>
       <c r="E16" t="n">
-        <v>5.9475</v>
+        <v>1.8582</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.3104</v>
+        <v>1.0674</v>
       </c>
       <c r="G16" t="n">
-        <v>5.7102</v>
+        <v>0.0127</v>
       </c>
       <c r="H16" t="n">
-        <v>1.0184</v>
+        <v>-1.8859</v>
       </c>
       <c r="I16" t="n">
-        <v>4.6918</v>
+        <v>1.8986</v>
       </c>
       <c r="J16" t="n">
-        <v>7.0776</v>
+        <v>1.5865</v>
       </c>
       <c r="K16" t="n">
-        <v>1.4126</v>
+        <v>-1.8322</v>
       </c>
       <c r="L16" t="n">
-        <v>5.6651</v>
+        <v>3.4187</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.3674</v>
+        <v>-1.5739</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.3942</v>
+        <v>-0.0537</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.9732</v>
+        <v>-1.5202</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.193</v>
+        <v>2.5091</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.9301</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.7371</v>
+        <v>2.5091</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.9379</v>
+        <v>0.6897</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.7139</v>
+        <v>0.2717</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2241</v>
+        <v>0.418</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.9421</v>
+        <v>-0.2859</v>
       </c>
       <c r="W16" t="n">
-        <v>1.5138</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-2.4559</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>I. CHACON RODRIGUEZ</t>
+          <t>M. NDIAYE SOW</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.9386</v>
+        <v>2.7419</v>
       </c>
       <c r="E17" t="n">
-        <v>2.0585</v>
+        <v>4.19</v>
       </c>
       <c r="F17" t="n">
-        <v>0.88</v>
+        <v>-1.448</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0127</v>
+        <v>-1.7472</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.8859</v>
+        <v>-0.2463</v>
       </c>
       <c r="I17" t="n">
-        <v>1.8986</v>
+        <v>-1.5009</v>
       </c>
       <c r="J17" t="n">
-        <v>1.5865</v>
+        <v>-0.3262</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.8322</v>
+        <v>0.3414</v>
       </c>
       <c r="L17" t="n">
-        <v>3.4187</v>
+        <v>-0.6676</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.5739</v>
+        <v>-1.421</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.0537</v>
+        <v>-0.5878</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.5202</v>
+        <v>-0.8333</v>
       </c>
       <c r="P17" t="n">
-        <v>2.5091</v>
+        <v>-0.772</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.9301</v>
       </c>
       <c r="R17" t="n">
-        <v>2.5091</v>
+        <v>1.158</v>
       </c>
       <c r="S17" t="n">
-        <v>0.7026</v>
+        <v>0.3493</v>
       </c>
       <c r="T17" t="n">
-        <v>0.472</v>
+        <v>0.0205</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2307</v>
+        <v>0.3288</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.2859</v>
+        <v>4.9119</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>6.4257</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.2859</v>
+        <v>-1.5138</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.542</v>
+        <v>1.0459</v>
       </c>
       <c r="E18" t="n">
-        <v>0.4495</v>
+        <v>-0.7522</v>
       </c>
       <c r="F18" t="n">
-        <v>2.0925</v>
+        <v>1.7981</v>
       </c>
       <c r="G18" t="n">
         <v>-3.1175</v>
@@ -1858,13 +1858,13 @@
         <v>1.9301</v>
       </c>
       <c r="S18" t="n">
-        <v>2.7874</v>
+        <v>1.2912</v>
       </c>
       <c r="T18" t="n">
-        <v>1.9262</v>
+        <v>0.7245</v>
       </c>
       <c r="U18" t="n">
-        <v>0.8612</v>
+        <v>0.5668</v>
       </c>
       <c r="V18" t="n">
         <v>0.9421</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1637</v>
+        <v>0.0233</v>
       </c>
       <c r="E19" t="n">
         <v>-0.0595</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.1043</v>
+        <v>0.0828</v>
       </c>
       <c r="G19" t="n">
         <v>0.1271</v>
@@ -1936,13 +1936,13 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2908</v>
+        <v>-0.1038</v>
       </c>
       <c r="T19" t="n">
         <v>-0.0595</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2313</v>
+        <v>-0.0443</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. ERRASTI UGARTE</t>
+          <t>B. MENDIA SANGRONIZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.612</v>
+        <v>-0.5357</v>
       </c>
       <c r="E20" t="n">
-        <v>0.6852</v>
+        <v>0.6758999999999999</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.2972</v>
+        <v>-1.2116</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.3357</v>
+        <v>-1.9755</v>
       </c>
       <c r="H20" t="n">
-        <v>0.9781</v>
+        <v>-0.2297</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.3138</v>
+        <v>-1.7458</v>
       </c>
       <c r="J20" t="n">
-        <v>1.3395</v>
+        <v>0.6</v>
       </c>
       <c r="K20" t="n">
-        <v>1.9664</v>
+        <v>0.6985</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.6269</v>
+        <v>-0.0985</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.6752</v>
+        <v>-2.5755</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.9883</v>
+        <v>-0.9283</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.6869</v>
+        <v>-1.6473</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.579</v>
+        <v>0.386</v>
       </c>
       <c r="Q20" t="n">
         <v>-0.965</v>
       </c>
       <c r="R20" t="n">
-        <v>0.386</v>
+        <v>1.3511</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3027</v>
+        <v>-0.1742</v>
       </c>
       <c r="T20" t="n">
-        <v>0.3107</v>
+        <v>-0.4729</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.007900000000000001</v>
+        <v>0.2987</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.228</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.5138</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>B. MENDIA SANGRONIZ</t>
+          <t>M. ERRASTI UGARTE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.7554999999999999</v>
+        <v>-0.7587</v>
       </c>
       <c r="E21" t="n">
-        <v>0.3755</v>
+        <v>0.4849</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.131</v>
+        <v>-1.2436</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.9755</v>
+        <v>-0.3357</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.2297</v>
+        <v>0.9781</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.7458</v>
+        <v>-1.3138</v>
       </c>
       <c r="J21" t="n">
-        <v>0.6</v>
+        <v>1.3395</v>
       </c>
       <c r="K21" t="n">
-        <v>0.6985</v>
+        <v>1.9664</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.0985</v>
+        <v>-0.6269</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.5755</v>
+        <v>-1.6752</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.9283</v>
+        <v>-0.9883</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.6473</v>
+        <v>-0.6869</v>
       </c>
       <c r="P21" t="n">
-        <v>0.386</v>
+        <v>-0.579</v>
       </c>
       <c r="Q21" t="n">
         <v>-0.965</v>
       </c>
       <c r="R21" t="n">
-        <v>1.3511</v>
+        <v>0.386</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.394</v>
+        <v>0.156</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7733</v>
+        <v>0.1104</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3794</v>
+        <v>0.0456</v>
       </c>
       <c r="V21" t="n">
-        <v>1.228</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.5138</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.2859</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.7066</v>
+        <v>-1.7511</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.2357</v>
+        <v>-1.735</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.4709</v>
+        <v>-0.0162</v>
       </c>
       <c r="G22" t="n">
         <v>-4.4594</v>
@@ -2170,13 +2170,13 @@
         <v>1.3511</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.8262</v>
+        <v>0.1292</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6253</v>
+        <v>-0.1246</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.201</v>
+        <v>0.2538</v>
       </c>
       <c r="V22" t="n">
         <v>1.228</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.0475</v>
+        <v>-3.4797</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.282</v>
+        <v>-2.9816</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.7655</v>
+        <v>-0.4981</v>
       </c>
       <c r="G23" t="n">
         <v>-1.7466</v>
@@ -2248,13 +2248,13 @@
         <v>1.3511</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.7568</v>
+        <v>-0.189</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5354</v>
+        <v>-0.235</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2214</v>
+        <v>0.0459</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,19 +2281,19 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>16.4904</v>
+        <v>17.1581</v>
       </c>
       <c r="E24" t="n">
-        <v>18.5724</v>
+        <v>18.5723</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.082100000000001</v>
+        <v>-1.4144</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.2301999999999982</v>
+        <v>-0.2302</v>
       </c>
       <c r="H24" t="n">
-        <v>5.1748</v>
+        <v>5.174800000000001</v>
       </c>
       <c r="I24" t="n">
         <v>-5.4053</v>
@@ -2302,10 +2302,10 @@
         <v>14.7119</v>
       </c>
       <c r="K24" t="n">
-        <v>9.049599999999998</v>
+        <v>9.0496</v>
       </c>
       <c r="L24" t="n">
-        <v>5.662399999999999</v>
+        <v>5.6624</v>
       </c>
       <c r="M24" t="n">
         <v>-14.9422</v>
@@ -2326,13 +2326,13 @@
         <v>15.4408</v>
       </c>
       <c r="S24" t="n">
-        <v>2.597799999999999</v>
+        <v>3.2651</v>
       </c>
       <c r="T24" t="n">
-        <v>0.3507000000000001</v>
+        <v>0.3504999999999999</v>
       </c>
       <c r="U24" t="n">
-        <v>2.2472</v>
+        <v>2.9146</v>
       </c>
       <c r="V24" t="n">
         <v>7.3679</v>
